--- a/artfynd/A 38695-2021 artfynd.xlsx
+++ b/artfynd/A 38695-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38695-2021 artfynd.xlsx
+++ b/artfynd/A 38695-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74471970</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549601.5646152911</v>
+        <v>549602</v>
       </c>
       <c r="R2" t="n">
-        <v>6246572.356111059</v>
+        <v>6246572</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74471301</v>
       </c>
       <c r="B3" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549601.5646152911</v>
+        <v>549602</v>
       </c>
       <c r="R3" t="n">
-        <v>6246572.356111059</v>
+        <v>6246572</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1988-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 38695-2021 artfynd.xlsx
+++ b/artfynd/A 38695-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471970</v>
       </c>
       <c r="B2" t="n">
-        <v>100773</v>
+        <v>100779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74471301</v>
       </c>
       <c r="B3" t="n">
-        <v>110493</v>
+        <v>110502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38695-2021 artfynd.xlsx
+++ b/artfynd/A 38695-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471970</v>
       </c>
       <c r="B2" t="n">
-        <v>100779</v>
+        <v>100780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74471301</v>
       </c>
       <c r="B3" t="n">
-        <v>110502</v>
+        <v>110507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38695-2021 artfynd.xlsx
+++ b/artfynd/A 38695-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471970</v>
       </c>
       <c r="B2" t="n">
-        <v>100780</v>
+        <v>100807</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74471301</v>
       </c>
       <c r="B3" t="n">
-        <v>110507</v>
+        <v>110535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38695-2021 artfynd.xlsx
+++ b/artfynd/A 38695-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471970</v>
       </c>
       <c r="B2" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74471301</v>
       </c>
       <c r="B3" t="n">
-        <v>110535</v>
+        <v>110541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38695-2021 artfynd.xlsx
+++ b/artfynd/A 38695-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471970</v>
       </c>
       <c r="B2" t="n">
-        <v>100813</v>
+        <v>100820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74471301</v>
       </c>
       <c r="B3" t="n">
-        <v>110541</v>
+        <v>110548</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38695-2021 artfynd.xlsx
+++ b/artfynd/A 38695-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471970</v>
       </c>
       <c r="B2" t="n">
-        <v>100820</v>
+        <v>100824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74471301</v>
       </c>
       <c r="B3" t="n">
-        <v>110548</v>
+        <v>110552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38695-2021 artfynd.xlsx
+++ b/artfynd/A 38695-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471970</v>
       </c>
       <c r="B2" t="n">
-        <v>100824</v>
+        <v>100831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74471301</v>
       </c>
       <c r="B3" t="n">
-        <v>110552</v>
+        <v>110560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38695-2021 artfynd.xlsx
+++ b/artfynd/A 38695-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471970</v>
       </c>
       <c r="B2" t="n">
-        <v>100834</v>
+        <v>100839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74471301</v>
       </c>
       <c r="B3" t="n">
-        <v>110563</v>
+        <v>110568</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38695-2021 artfynd.xlsx
+++ b/artfynd/A 38695-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471970</v>
       </c>
       <c r="B2" t="n">
-        <v>100839</v>
+        <v>100847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74471301</v>
       </c>
       <c r="B3" t="n">
-        <v>110568</v>
+        <v>110576</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38695-2021 artfynd.xlsx
+++ b/artfynd/A 38695-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74471970</v>
       </c>
       <c r="B2" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74471301</v>
       </c>
       <c r="B3" t="n">
-        <v>110576</v>
+        <v>110586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 38695-2021 artfynd.xlsx
+++ b/artfynd/A 38695-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74471970</v>
+        <v>74471301</v>
       </c>
       <c r="B2" t="n">
-        <v>100857</v>
+        <v>111175</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 3F9j 3148. SOM: Hepatica nobilis. LEG: Thomas Karlsson</t>
+          <t>Smålands flora 2007: KOO: 3F9j 3148. SOM: Hedera helix. LEG: Thomas Karlsson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Granskogssluttning</t>
+          <t>Granskogssluttning (synes vild)</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74471301</v>
+        <v>74471970</v>
       </c>
       <c r="B3" t="n">
-        <v>110586</v>
+        <v>101325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 3F9j 3148. SOM: Hedera helix. LEG: Thomas Karlsson</t>
+          <t>Smålands flora 2007: KOO: 3F9j 3148. SOM: Hepatica nobilis. LEG: Thomas Karlsson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Granskogssluttning (synes vild)</t>
+          <t>Granskogssluttning</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
